--- a/Automatizacion Envio Masivo de Correos/contactos_catalan_ronda2.xlsx
+++ b/Automatizacion Envio Masivo de Correos/contactos_catalan_ronda2.xlsx
@@ -4013,6 +4013,11 @@
           <t>Tarragona</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>info@soldeges.com</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>https://fontgestoria.com/</t>
@@ -4035,6 +4040,11 @@
           <t>Tarragona</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>gestoria@campdepadros.cat</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>http://www.campdepadros.cat/contacte.php</t>
@@ -4057,6 +4067,11 @@
           <t>Tarragona</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>info@habirent2005.com</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>https://www.gestorias.es/tarragona/43004</t>
@@ -4101,6 +4116,11 @@
           <t>Tarragona</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>asde@asdeonline.com</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>https://www.asdeonline.com/</t>
@@ -4121,6 +4141,11 @@
       <c r="C114" t="inlineStr">
         <is>
           <t>Tarragona</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>info@vivesiroig.cat</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
